--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G642"/>
+  <dimension ref="A1:G647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17674,16 +17674,16 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>191.21</v>
+        <v>204.99</v>
       </c>
       <c r="C641" t="n">
-        <v>195.4</v>
+        <v>210.22</v>
       </c>
       <c r="D641" t="n">
         <v>210.67</v>
       </c>
       <c r="E641" t="n">
-        <v>218.77</v>
+        <v>215.69</v>
       </c>
       <c r="F641" t="n">
         <v>199.89</v>
@@ -17701,21 +17701,156 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>179.01</v>
+        <v>204.99</v>
       </c>
       <c r="C642" t="n">
-        <v>181.64</v>
+        <v>210.22</v>
       </c>
       <c r="D642" t="n">
         <v>208.02</v>
       </c>
       <c r="E642" t="n">
-        <v>218.77</v>
+        <v>215.69</v>
       </c>
       <c r="F642" t="n">
         <v>196.64</v>
       </c>
       <c r="G642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="C643" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="D643" t="n">
+        <v>205.31</v>
+      </c>
+      <c r="E643" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="F643" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>203.01</v>
+      </c>
+      <c r="C644" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="D644" t="n">
+        <v>204.37</v>
+      </c>
+      <c r="E644" t="n">
+        <v>212.3</v>
+      </c>
+      <c r="F644" t="n">
+        <v>190.87</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>187.94</v>
+      </c>
+      <c r="C645" t="n">
+        <v>205.21</v>
+      </c>
+      <c r="D645" t="n">
+        <v>201.91</v>
+      </c>
+      <c r="E645" t="n">
+        <v>209.98</v>
+      </c>
+      <c r="F645" t="n">
+        <v>185.11</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="C646" t="n">
+        <v>205.21</v>
+      </c>
+      <c r="D646" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="E646" t="n">
+        <v>211.52</v>
+      </c>
+      <c r="F646" t="n">
+        <v>185.11</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="C647" t="n">
+        <v>203.89</v>
+      </c>
+      <c r="D647" t="n">
+        <v>203.29</v>
+      </c>
+      <c r="E647" t="n">
+        <v>211.52</v>
+      </c>
+      <c r="F647" t="n">
+        <v>181.54</v>
+      </c>
+      <c r="G647" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17732,7 +17867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25075,6 +25210,56 @@
       </c>
       <c r="B734" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -25237,28 +25422,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1697254237666881</v>
+        <v>-0.1645559803266918</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002146664165753376</v>
+        <v>0.00204577970311548</v>
       </c>
       <c r="M2" t="n">
-        <v>19.78203849782074</v>
+        <v>19.74362483341589</v>
       </c>
       <c r="N2" t="n">
-        <v>801.0934558117933</v>
+        <v>797.0960736419155</v>
       </c>
       <c r="O2" t="n">
-        <v>28.30359439738694</v>
+        <v>28.23288992720929</v>
       </c>
       <c r="P2" t="n">
-        <v>196.1807938605526</v>
+        <v>196.1283232539082</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25309,28 +25494,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5561808404409335</v>
+        <v>-0.5428025141046589</v>
       </c>
       <c r="J3" t="n">
+        <v>646</v>
+      </c>
+      <c r="K3" t="n">
         <v>641</v>
       </c>
-      <c r="K3" t="n">
-        <v>636</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.09808453576570819</v>
+        <v>0.0957455184026621</v>
       </c>
       <c r="M3" t="n">
-        <v>8.15273387896681</v>
+        <v>8.027180050319217</v>
       </c>
       <c r="N3" t="n">
-        <v>169.8607879313796</v>
+        <v>167.5958986296618</v>
       </c>
       <c r="O3" t="n">
-        <v>13.03306517789962</v>
+        <v>12.9458834626943</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1430871227019</v>
+        <v>220.0054430285578</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25381,28 +25566,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.345506975903624</v>
+        <v>-0.3611439939102222</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1298346294905227</v>
+        <v>0.1398804786045968</v>
       </c>
       <c r="M4" t="n">
-        <v>5.586549482518355</v>
+        <v>5.632533315208596</v>
       </c>
       <c r="N4" t="n">
-        <v>47.68394908328538</v>
+        <v>48.21179519081626</v>
       </c>
       <c r="O4" t="n">
-        <v>6.905356550047606</v>
+        <v>6.943471407791369</v>
       </c>
       <c r="P4" t="n">
-        <v>223.759716147806</v>
+        <v>223.9211184320309</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25453,28 +25638,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5303197996046429</v>
+        <v>0.5238974648714446</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.081155347164661</v>
+        <v>0.08054681609632519</v>
       </c>
       <c r="M5" t="n">
-        <v>10.10815730544023</v>
+        <v>10.04342308915585</v>
       </c>
       <c r="N5" t="n">
-        <v>190.0385149475887</v>
+        <v>188.6031523191178</v>
       </c>
       <c r="O5" t="n">
-        <v>13.78544576528408</v>
+        <v>13.73328628985495</v>
       </c>
       <c r="P5" t="n">
-        <v>200.7038013892918</v>
+        <v>200.7699951790466</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25525,28 +25710,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1214197228209297</v>
+        <v>-0.1266856056307827</v>
       </c>
       <c r="J6" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K6" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001342698700730893</v>
+        <v>0.001485185650805354</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8004259895385</v>
+        <v>20.66988638563717</v>
       </c>
       <c r="N6" t="n">
-        <v>645.8387750646839</v>
+        <v>640.9212483816041</v>
       </c>
       <c r="O6" t="n">
-        <v>25.41335820124298</v>
+        <v>25.31642250361619</v>
       </c>
       <c r="P6" t="n">
-        <v>193.7003684524775</v>
+        <v>193.7556505730006</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25584,7 +25769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G642"/>
+  <dimension ref="A1:G647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49167,12 +49352,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>-43.63052435314663,172.68586335868042</t>
+          <t>-43.63060688709535,172.6857358133822</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>-43.63108737023402,172.6864841380966</t>
+          <t>-43.631176116621695,172.68634694517283</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -49182,7 +49367,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>-43.63230316150269,172.6875869659422</t>
+          <t>-43.63228471370407,172.6876154741613</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -49204,12 +49389,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>-43.63045128233119,172.68597627948054</t>
+          <t>-43.63060688709535,172.6857358133822</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>-43.63100497127899,172.6866115179398</t>
+          <t>-43.631176116621695,172.68634694517283</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -49219,7 +49404,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>-43.63230316150269,172.6875869659422</t>
+          <t>-43.63228471370407,172.6876154741613</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
@@ -49228,6 +49413,191 @@
         </is>
       </c>
       <c r="G642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-43.63060185600247,172.68574358828698</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-43.63115940931857,172.6863727730213</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-43.63168462698356,172.68705196478018</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-43.63227069816391,172.68763713299145</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-43.632678928736,172.68849711303938</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-43.63059502808984,172.68575413994142</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-43.63115940931857,172.6863727730213</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-43.63167899794721,172.6870606666457</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-43.632264409138145,172.687646851694</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-43.632673957353454,172.68850479542417</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-43.63050476778344,172.68589362518398</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-43.63114611533122,172.68639332420236</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-43.63166426663621,172.68708343960517</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-43.63225051338296,172.68766832539154</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-43.63263945714193,172.68855810928852</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-43.6304356499535,172.6860004370916</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-43.63114611533122,172.68639332420236</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-43.6316729497266,172.68707001652066</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-43.632259737289864,172.68765407130033</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-43.63263945714193,172.68855810928852</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-43.63036880800419,172.68610373156332</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-43.63113821079641,172.68640554381918</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-43.63167253054296,172.6870706645317</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-43.632259737289864,172.68765407130033</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-43.63261807418564,172.68859115274674</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G647"/>
+  <dimension ref="A1:G649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>187.94</v>
+        <v>202.68</v>
       </c>
       <c r="C645" t="n">
         <v>205.21</v>
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>176.4</v>
+        <v>202.68</v>
       </c>
       <c r="C646" t="n">
         <v>205.21</v>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>165.24</v>
+        <v>202.68</v>
       </c>
       <c r="C647" t="n">
         <v>203.89</v>
@@ -17845,12 +17845,66 @@
         <v>203.29</v>
       </c>
       <c r="E647" t="n">
-        <v>211.52</v>
+        <v>209.49</v>
       </c>
       <c r="F647" t="n">
         <v>181.54</v>
       </c>
       <c r="G647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>202.82</v>
+      </c>
+      <c r="C648" t="n">
+        <v>207.07</v>
+      </c>
+      <c r="D648" t="n">
+        <v>205.91</v>
+      </c>
+      <c r="E648" t="n">
+        <v>211.37</v>
+      </c>
+      <c r="F648" t="n">
+        <v>178.69</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="C649" t="n">
+        <v>208.82</v>
+      </c>
+      <c r="D649" t="n">
+        <v>207.09</v>
+      </c>
+      <c r="E649" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="F649" t="n">
+        <v>178.85</v>
+      </c>
+      <c r="G649" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17867,7 +17921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25260,6 +25314,26 @@
       </c>
       <c r="B739" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -25422,28 +25496,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1645559803266918</v>
+        <v>-0.1359255729893597</v>
       </c>
       <c r="J2" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K2" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00204577970311548</v>
+        <v>0.001406938504844746</v>
       </c>
       <c r="M2" t="n">
-        <v>19.74362483341589</v>
+        <v>19.61836919876809</v>
       </c>
       <c r="N2" t="n">
-        <v>797.0960736419155</v>
+        <v>794.0199051474386</v>
       </c>
       <c r="O2" t="n">
-        <v>28.23288992720929</v>
+        <v>28.17835880862189</v>
       </c>
       <c r="P2" t="n">
-        <v>196.1283232539082</v>
+        <v>195.8333760810007</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25494,28 +25568,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5428025141046589</v>
+        <v>-0.54131589295395</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K3" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0957455184026621</v>
+        <v>0.09582174396793586</v>
       </c>
       <c r="M3" t="n">
-        <v>8.027180050319217</v>
+        <v>8.006444971199148</v>
       </c>
       <c r="N3" t="n">
-        <v>167.5958986296618</v>
+        <v>167.0975002334968</v>
       </c>
       <c r="O3" t="n">
-        <v>12.9458834626943</v>
+        <v>12.92661983016043</v>
       </c>
       <c r="P3" t="n">
-        <v>220.0054430285578</v>
+        <v>219.9900280619797</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25566,28 +25640,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3611439939102222</v>
+        <v>-0.365571764197559</v>
       </c>
       <c r="J4" t="n">
+        <v>648</v>
+      </c>
+      <c r="K4" t="n">
         <v>646</v>
       </c>
-      <c r="K4" t="n">
-        <v>644</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1398804786045968</v>
+        <v>0.1431738632831459</v>
       </c>
       <c r="M4" t="n">
-        <v>5.632533315208596</v>
+        <v>5.640660413614988</v>
       </c>
       <c r="N4" t="n">
-        <v>48.21179519081626</v>
+        <v>48.24458565397482</v>
       </c>
       <c r="O4" t="n">
-        <v>6.943471407791369</v>
+        <v>6.945832250635975</v>
       </c>
       <c r="P4" t="n">
-        <v>223.9211184320309</v>
+        <v>223.9669911838741</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25638,28 +25712,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5238974648714446</v>
+        <v>0.5219279565014169</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K5" t="n">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08054681609632519</v>
+        <v>0.08045207752891159</v>
       </c>
       <c r="M5" t="n">
-        <v>10.04342308915585</v>
+        <v>10.02236062601899</v>
       </c>
       <c r="N5" t="n">
-        <v>188.6031523191178</v>
+        <v>188.0672274106948</v>
       </c>
       <c r="O5" t="n">
-        <v>13.73328628985495</v>
+        <v>13.71376051310124</v>
       </c>
       <c r="P5" t="n">
-        <v>200.7699951790466</v>
+        <v>200.79037354481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25710,28 +25784,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1266856056307827</v>
+        <v>-0.1334775102094185</v>
       </c>
       <c r="J6" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K6" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001485185650805354</v>
+        <v>0.001658113445052511</v>
       </c>
       <c r="M6" t="n">
-        <v>20.66988638563717</v>
+        <v>20.642212749186</v>
       </c>
       <c r="N6" t="n">
-        <v>640.9212483816041</v>
+        <v>639.3099795161212</v>
       </c>
       <c r="O6" t="n">
-        <v>25.31642250361619</v>
+        <v>25.28457987620362</v>
       </c>
       <c r="P6" t="n">
-        <v>193.7556505730006</v>
+        <v>193.8271420044397</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25769,7 +25843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G647"/>
+  <dimension ref="A1:G649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49500,7 +49574,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>-43.63050476778344,172.68589362518398</t>
+          <t>-43.63059305158862,172.68575719436728</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -49537,7 +49611,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>-43.6304356499535,172.6860004370916</t>
+          <t>-43.63059305158862,172.68575719436728</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -49574,7 +49648,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>-43.63036880800419,172.68610373156332</t>
+          <t>-43.63059305158862,172.68575719436728</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -49589,7 +49663,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>-43.632259737289864,172.68765407130033</t>
+          <t>-43.63224757850311,172.68767286078332</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -49598,6 +49672,80 @@
         </is>
       </c>
       <c r="G647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-43.630593890104294,172.68575589855027</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-43.6311572535371,172.68637610564585</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-43.631688219985115,172.68704641039713</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-43.63225883885746,172.68765545968603</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-43.63260100375141,172.6886175319613</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-43.63059047614754,172.68576117437638</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-43.631167733029486,172.68635990538533</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-43.63169528622071,172.68703548677513</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-43.63227219555088,172.68763481901436</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-43.63260196209172,172.68861605102333</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G649"/>
+  <dimension ref="A1:G652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17875,7 +17875,7 @@
         <v>211.37</v>
       </c>
       <c r="F648" t="n">
-        <v>178.69</v>
+        <v>176.98</v>
       </c>
       <c r="G648" t="inlineStr">
         <is>
@@ -17902,9 +17902,90 @@
         <v>213.6</v>
       </c>
       <c r="F649" t="n">
-        <v>178.85</v>
+        <v>174.74</v>
       </c>
       <c r="G649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="C650" t="n">
+        <v>208.66</v>
+      </c>
+      <c r="D650" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="E650" t="n">
+        <v>212.74</v>
+      </c>
+      <c r="F650" t="n">
+        <v>172</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>202.35</v>
+      </c>
+      <c r="C651" t="n">
+        <v>207.58</v>
+      </c>
+      <c r="D651" t="n">
+        <v>205.79</v>
+      </c>
+      <c r="E651" t="n">
+        <v>212.82</v>
+      </c>
+      <c r="F651" t="n">
+        <v>169.99</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>202.52</v>
+      </c>
+      <c r="C652" t="n">
+        <v>207.96</v>
+      </c>
+      <c r="D652" t="n">
+        <v>206.45</v>
+      </c>
+      <c r="E652" t="n">
+        <v>212.61</v>
+      </c>
+      <c r="F652" t="n">
+        <v>170.52</v>
+      </c>
+      <c r="G652" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17921,7 +18002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B741"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25334,6 +25415,36 @@
       </c>
       <c r="B741" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -25496,28 +25607,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1359255729893597</v>
+        <v>-0.1268429417032093</v>
       </c>
       <c r="J2" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001406938504844746</v>
+        <v>0.001236584878788971</v>
       </c>
       <c r="M2" t="n">
-        <v>19.61836919876809</v>
+        <v>19.55195837326357</v>
       </c>
       <c r="N2" t="n">
-        <v>794.0199051474386</v>
+        <v>790.8753972817702</v>
       </c>
       <c r="O2" t="n">
-        <v>28.17835880862189</v>
+        <v>28.12250695229304</v>
       </c>
       <c r="P2" t="n">
-        <v>195.8333760810007</v>
+        <v>195.7392964997534</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25568,28 +25679,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.54131589295395</v>
+        <v>-0.5389924772590156</v>
       </c>
       <c r="J3" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09582174396793586</v>
+        <v>0.09590099662473439</v>
       </c>
       <c r="M3" t="n">
-        <v>8.006444971199148</v>
+        <v>7.975792953814424</v>
       </c>
       <c r="N3" t="n">
-        <v>167.0975002334968</v>
+        <v>166.3559646949361</v>
       </c>
       <c r="O3" t="n">
-        <v>12.92661983016043</v>
+        <v>12.89790543828478</v>
       </c>
       <c r="P3" t="n">
-        <v>219.9900280619797</v>
+        <v>219.9658670527214</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25640,28 +25751,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.365571764197559</v>
+        <v>-0.3721239439637909</v>
       </c>
       <c r="J4" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="K4" t="n">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1431738632831459</v>
+        <v>0.1481171324352225</v>
       </c>
       <c r="M4" t="n">
-        <v>5.640660413614988</v>
+        <v>5.652385021233747</v>
       </c>
       <c r="N4" t="n">
-        <v>48.24458565397482</v>
+        <v>48.28859206958049</v>
       </c>
       <c r="O4" t="n">
-        <v>6.945832250635975</v>
+        <v>6.94899935743129</v>
       </c>
       <c r="P4" t="n">
-        <v>223.9669911838741</v>
+        <v>224.0351080183588</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25712,28 +25823,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5219279565014169</v>
+        <v>0.5200588273356451</v>
       </c>
       <c r="J5" t="n">
+        <v>651</v>
+      </c>
+      <c r="K5" t="n">
         <v>648</v>
       </c>
-      <c r="K5" t="n">
-        <v>645</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.08045207752891159</v>
+        <v>0.0806334401861819</v>
       </c>
       <c r="M5" t="n">
-        <v>10.02236062601899</v>
+        <v>9.985399175452688</v>
       </c>
       <c r="N5" t="n">
-        <v>188.0672274106948</v>
+        <v>187.2182503337181</v>
       </c>
       <c r="O5" t="n">
-        <v>13.71376051310124</v>
+        <v>13.68277202666616</v>
       </c>
       <c r="P5" t="n">
-        <v>200.79037354481</v>
+        <v>200.8097953137515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25784,28 +25895,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1334775102094185</v>
+        <v>-0.1521000299572447</v>
       </c>
       <c r="J6" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="K6" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001658113445052511</v>
+        <v>0.002166280261951981</v>
       </c>
       <c r="M6" t="n">
-        <v>20.642212749186</v>
+        <v>20.64722653823817</v>
       </c>
       <c r="N6" t="n">
-        <v>639.3099795161212</v>
+        <v>638.2764505340512</v>
       </c>
       <c r="O6" t="n">
-        <v>25.28457987620362</v>
+        <v>25.2641336786768</v>
       </c>
       <c r="P6" t="n">
-        <v>193.8271420044397</v>
+        <v>194.0237741631002</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25843,7 +25954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G649"/>
+  <dimension ref="A1:G652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49705,7 +49816,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>-43.63260100375141,172.6886175319613</t>
+          <t>-43.63259076148788,172.68863335948288</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -49742,10 +49853,121 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>-43.63260196209172,172.68861605102333</t>
+          <t>-43.632577344718264,172.6886540926024</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-43.630597962894505,172.68574960458147</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-43.63116677490456,172.68636138655222</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-43.63169534610405,172.68703539420204</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-43.63226704453951,172.68764277909509</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-43.632560933128815,172.68867945363786</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-43.630591075087345,172.68576024879292</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-43.63116030756083,172.68637138442767</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-43.631687501384825,172.68704752127377</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-43.63226752370339,172.68764203862253</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-43.63254889396651,172.68869805789234</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-43.63059209328499,172.68575867530095</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-43.631162583107795,172.68636786665692</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-43.63169145368627,172.68704141145176</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-43.63226626589821,172.687643982363</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-43.632552068472286,172.68869315229364</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
